--- a/data/datos_reales/xlsx/DatosReales_CICES_Proyectos.xlsx
+++ b/data/datos_reales/xlsx/DatosReales_CICES_Proyectos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\angie\IdeaProjects\cices-system\data\datos_reales\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C53AD369-53C6-4203-99B4-0183B192A5C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D83E387-E322-439B-B4EF-C4500A8E52EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7488" yWindow="384" windowWidth="14280" windowHeight="11856" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PROYECTO" sheetId="1" r:id="rId1"/>
@@ -1526,9 +1526,7 @@
       <c r="D7" s="5">
         <v>41</v>
       </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
+      <c r="E7" s="2"/>
       <c r="F7" s="2" t="s">
         <v>68</v>
       </c>
@@ -1718,9 +1716,7 @@
       <c r="D13" s="5">
         <v>41</v>
       </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
+      <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
         <v>68</v>
       </c>
@@ -1739,6 +1735,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/data/datos_reales/xlsx/DatosReales_CICES_Proyectos.xlsx
+++ b/data/datos_reales/xlsx/DatosReales_CICES_Proyectos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\angie\IdeaProjects\cices-system\data\datos_reales\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D83E387-E322-439B-B4EF-C4500A8E52EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77027E2D-52D1-42FD-9D44-143E23908468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7488" yWindow="384" windowWidth="14280" windowHeight="11856" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PROYECTO" sheetId="1" r:id="rId1"/>
@@ -616,9 +616,7 @@
       <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="2">
-        <v>19</v>
-      </c>
+      <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
         <v>14</v>
       </c>
@@ -648,9 +646,7 @@
       <c r="E3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="2">
-        <v>19</v>
-      </c>
+      <c r="F3" s="2"/>
       <c r="G3" s="2" t="s">
         <v>19</v>
       </c>

--- a/data/datos_reales/xlsx/DatosReales_CICES_Proyectos.xlsx
+++ b/data/datos_reales/xlsx/DatosReales_CICES_Proyectos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\angie\IdeaProjects\cices-system\data\datos_reales\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77027E2D-52D1-42FD-9D44-143E23908468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C0FD21D-880E-485D-9F03-B93541949203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4080" yWindow="384" windowWidth="14280" windowHeight="11856" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PROYECTO" sheetId="1" r:id="rId1"/>
@@ -1911,7 +1911,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.44140625" customWidth="1"/>
@@ -2060,106 +2060,6 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2">
-        <v>12</v>
-      </c>
-      <c r="D8" s="2">
-        <v>37</v>
-      </c>
-      <c r="E8" s="2">
-        <v>10</v>
-      </c>
-      <c r="F8" s="2">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2">
-        <v>5</v>
-      </c>
-      <c r="C9" s="2">
-        <v>12</v>
-      </c>
-      <c r="D9" s="2">
-        <v>36</v>
-      </c>
-      <c r="E9" s="2">
-        <v>5</v>
-      </c>
-      <c r="F9" s="2">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2">
-        <v>6</v>
-      </c>
-      <c r="C10" s="2">
-        <v>12</v>
-      </c>
-      <c r="D10" s="2">
-        <v>36</v>
-      </c>
-      <c r="E10" s="2">
-        <v>5</v>
-      </c>
-      <c r="F10" s="2">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2">
-        <v>5</v>
-      </c>
-      <c r="C11" s="2">
-        <v>12</v>
-      </c>
-      <c r="D11" s="2">
-        <v>36</v>
-      </c>
-      <c r="E11" s="2">
-        <v>5</v>
-      </c>
-      <c r="F11" s="2">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2">
-        <v>12</v>
-      </c>
-      <c r="D12" s="2">
-        <v>36</v>
-      </c>
-      <c r="E12" s="2">
-        <v>5</v>
-      </c>
-      <c r="F12" s="2">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/datos_reales/xlsx/DatosReales_CICES_Proyectos.xlsx
+++ b/data/datos_reales/xlsx/DatosReales_CICES_Proyectos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\angie\IdeaProjects\cices-system\data\datos_reales\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C0FD21D-880E-485D-9F03-B93541949203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADB86FC1-1AE1-45EA-9C3C-1D185D5E8260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4080" yWindow="384" windowWidth="14280" windowHeight="11856" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PROYECTO" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="132">
   <si>
     <t>ID_PROYECTO</t>
   </si>
@@ -274,6 +274,156 @@
   </si>
   <si>
     <t>ID_CODIGO_TIPO_MODALIDAD</t>
+  </si>
+  <si>
+    <t>DEMO001</t>
+  </si>
+  <si>
+    <t>Proyecto de Ejemplo en Salud Digital</t>
+  </si>
+  <si>
+    <t>Proyecto de prueba para validación del módulo de proyectos</t>
+  </si>
+  <si>
+    <t>Validar el registro de proyectos de investigación</t>
+  </si>
+  <si>
+    <t>Salud Digital</t>
+  </si>
+  <si>
+    <t>TEST002</t>
+  </si>
+  <si>
+    <t>Sistema Piloto de Investigación Académica</t>
+  </si>
+  <si>
+    <t>Simulación de datos para ambiente de desarrollo</t>
+  </si>
+  <si>
+    <t>Probar funcionalidades de mantenimiento de proyectos</t>
+  </si>
+  <si>
+    <t>Educación e Innovación</t>
+  </si>
+  <si>
+    <t>MOCK003</t>
+  </si>
+  <si>
+    <t>Análisis Experimental Sociocultural</t>
+  </si>
+  <si>
+    <t>Registro ficticio para pruebas de reportes</t>
+  </si>
+  <si>
+    <t>Evaluar comportamiento de filtros y consultas</t>
+  </si>
+  <si>
+    <t>Ciencias Sociales</t>
+  </si>
+  <si>
+    <t>DEMO004</t>
+  </si>
+  <si>
+    <t>Plataforma de Datos Biomédicos</t>
+  </si>
+  <si>
+    <t>Proyecto demostrativo para integración de módulos</t>
+  </si>
+  <si>
+    <t>Simular proyectos biomédicos intervencionales</t>
+  </si>
+  <si>
+    <t>Biomedicina</t>
+  </si>
+  <si>
+    <t>TEST005</t>
+  </si>
+  <si>
+    <t>Estudio de Ejemplo Ambiental</t>
+  </si>
+  <si>
+    <t>Datos de muestra para exportación de documentos</t>
+  </si>
+  <si>
+    <t>Verificar exportación de reportes PDF y Word</t>
+  </si>
+  <si>
+    <t>Ambiente y Desarrollo</t>
+  </si>
+  <si>
+    <t>MOCK006</t>
+  </si>
+  <si>
+    <t>Investigación de Prueba en IA</t>
+  </si>
+  <si>
+    <t>Proyecto ficticio orientado a inteligencia artificial</t>
+  </si>
+  <si>
+    <t>Validar carga y visualización de información</t>
+  </si>
+  <si>
+    <t>Inteligencia Artificial</t>
+  </si>
+  <si>
+    <t>DEMO007</t>
+  </si>
+  <si>
+    <t>Modelo Experimental Educativo</t>
+  </si>
+  <si>
+    <t>Proyecto de ejemplo para pruebas QA</t>
+  </si>
+  <si>
+    <t>Confirmar funcionamiento de formularios dinámicos</t>
+  </si>
+  <si>
+    <t>Tecnología Educativa</t>
+  </si>
+  <si>
+    <t>TEST008</t>
+  </si>
+  <si>
+    <t>Simulación de Proyecto Clínico</t>
+  </si>
+  <si>
+    <t>Información de prueba para módulo clínico</t>
+  </si>
+  <si>
+    <t>Evaluar integridad de datos registrados</t>
+  </si>
+  <si>
+    <t>Salud Pública</t>
+  </si>
+  <si>
+    <t>MOCK009</t>
+  </si>
+  <si>
+    <t>Proyecto Base de Investigación Marina</t>
+  </si>
+  <si>
+    <t>Datos ficticios para ambiente de testing</t>
+  </si>
+  <si>
+    <t>Probar consultas avanzadas y exportaciones</t>
+  </si>
+  <si>
+    <t>Biología Marina</t>
+  </si>
+  <si>
+    <t>DEMO010</t>
+  </si>
+  <si>
+    <t>Caso de Uso para Ciencia de Datos</t>
+  </si>
+  <si>
+    <t>Proyecto de ejemplo orientado a Big Data</t>
+  </si>
+  <si>
+    <t>Simular escenarios de investigación científica</t>
+  </si>
+  <si>
+    <t>Ciencia de Datos</t>
   </si>
 </sst>
 </file>
@@ -324,7 +474,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -334,6 +484,12 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -553,7 +709,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.88671875" customWidth="1"/>
@@ -658,6 +814,306 @@
       </c>
       <c r="J3" s="3">
         <v>46112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="H4" s="6">
+        <v>15</v>
+      </c>
+      <c r="I4" s="7">
+        <v>45292</v>
+      </c>
+      <c r="J4" s="7">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H5" s="6">
+        <v>18</v>
+      </c>
+      <c r="I5" s="7">
+        <v>45337</v>
+      </c>
+      <c r="J5" s="7">
+        <v>46433</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="H6" s="6">
+        <v>17</v>
+      </c>
+      <c r="I6" s="7">
+        <v>44256</v>
+      </c>
+      <c r="J6" s="7">
+        <v>45626</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="H7" s="6">
+        <v>16</v>
+      </c>
+      <c r="I7" s="7">
+        <v>45056</v>
+      </c>
+      <c r="J7" s="7">
+        <v>46883</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="H8" s="6">
+        <v>18</v>
+      </c>
+      <c r="I8" s="7">
+        <v>44732</v>
+      </c>
+      <c r="J8" s="7">
+        <v>45828</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="H9" s="6">
+        <v>16</v>
+      </c>
+      <c r="I9" s="7">
+        <v>45540</v>
+      </c>
+      <c r="J9" s="7">
+        <v>46635</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H10" s="6">
+        <v>17</v>
+      </c>
+      <c r="I10" s="7">
+        <v>43831</v>
+      </c>
+      <c r="J10" s="7">
+        <v>45291</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H11" s="6">
+        <v>15</v>
+      </c>
+      <c r="I11" s="7">
+        <v>45394</v>
+      </c>
+      <c r="J11" s="7">
+        <v>46124</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="H12" s="6">
+        <v>15</v>
+      </c>
+      <c r="I12" s="7">
+        <v>45156</v>
+      </c>
+      <c r="J12" s="7">
+        <v>46617</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="H13" s="6">
+        <v>16</v>
+      </c>
+      <c r="I13" s="7">
+        <v>45778</v>
+      </c>
+      <c r="J13" s="7">
+        <v>47239</v>
       </c>
     </row>
   </sheetData>
